--- a/baselines/openvas/OpenVAS_bBWA.xlsx
+++ b/baselines/openvas/OpenVAS_bBWA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,92 +429,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>cvss</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>detection_method</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>detection_result</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>plugin_details</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>instances</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>impact</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>insight</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>log_method</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>plugin</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>port</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>product_detection_result</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>protocol</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>references</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>severity</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>solution</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -780,7 +792,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tiki Wiki CMS Groupware &lt; 4.2 Multiple Unspeci_x001C_ed Vulnerabilities</t>
+          <t>Tiki Wiki CMS Groupware &lt; 4.2 Multiple Unspecified Vulnerabilities</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -788,7 +800,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[Tiki Wiki CMS Groupware is prone to multiple unspeci_x001C_ed vulnerabilities, including: - An unspeci_x001C_ed SQL-injection vulnerability - An unspeci_x001C_ed authentication-bypass vulnerability - An unspeci_x001C_ed vulnerability']</t>
+          <t>[Tiki Wiki CMS Groupware is prone to multiple unspecified vulnerabilities, including: - An unspecified SQL-injection vulnerability - An unspecified authentication-bypass vulnerability - An unspecified vulnerability']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -864,7 +876,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PHP-CGI-based setups vulnerability when parsing query string parameters from php les.</t>
+          <t>PHP-CGI-based setups vulnerability when parsing query string parameters from php files.</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2546,7 +2558,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tiki Wiki CMS Groupware 'xedURLData' Local File Inclusion Vulnerability</t>
+          <t>Tiki Wiki CMS Groupware 'fixedURLData' Local File Inclusion Vulnerability</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2787,8 +2799,7 @@
       <c r="Q28" t="inlineStr">
         <is>
           <t>['Solution type: WillNotFix
-No known solution was made available for at least one year since the disclosure of this vulnera-
-bility. Likely none will be provided anymore. General solution options are to upgrade to a newer
+No known solution was made available for at least one year since the disclosure of this vulnerability. Likely none will be provided anymore. General solution options are to upgrade to a newer
 release, disable respective features, remove the product or replace the product by another one.']</t>
         </is>
       </c>
@@ -3607,7 +3618,7 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>21</v>
+        <v>2121</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -4488,7 +4499,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SSL/TLS: Certicate Expired</t>
+          <t>SSL/TLS: Certificate Expired</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -4788,7 +4799,7 @@
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>25</v>
+        <v>5432</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -4911,7 +4922,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>UnrealIRCd Authentication Spoong Vulnerability</t>
+          <t>UnrealIRCd Authentication Spoofing Vulnerability</t>
         </is>
       </c>
       <c r="B54" t="n">
